--- a/РАБОЧИЙ СТОЛ/расчет ПОКОМ КИ/дв 07,07,26 млрсч пок ки.xlsx
+++ b/РАБОЧИЙ СТОЛ/расчет ПОКОМ КИ/дв 07,07,26 млрсч пок ки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчет ПОКОМ КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23C52E8A-B601-4C37-B675-BF8D417DA3A9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9AA81F7-365B-4F1F-8AA4-D8B3F2EC166A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AD$114</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="181029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="257">
   <si>
     <t>Номенклатура</t>
   </si>
@@ -79,9 +79,6 @@
   </si>
   <si>
     <t>ср нов</t>
-  </si>
-  <si>
-    <t>расчет</t>
   </si>
   <si>
     <t>кон ост</t>
@@ -819,6 +816,12 @@
   <si>
     <t>159 шт списание (04,07,26 - инвентаризация)</t>
   </si>
+  <si>
+    <t>заказ</t>
+  </si>
+  <si>
+    <t>12,07,</t>
+  </si>
 </sst>
 </file>
 
@@ -1298,7 +1301,9 @@
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
+      <c r="R1" s="1">
+        <v>13.3</v>
+      </c>
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
@@ -1435,43 +1440,43 @@
         <v>15</v>
       </c>
       <c r="R3" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="S3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="2" t="s">
+      <c r="T3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="T3" s="2" t="s">
+      <c r="U3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="U3" s="2" t="s">
+      <c r="V3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="X3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AB3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="V3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="W3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="X3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="Y3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="Z3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AA3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AB3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AC3" s="2" t="s">
+      <c r="AD3" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="AD3" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="AE3" s="1"/>
       <c r="AF3" s="1"/>
@@ -1509,40 +1514,42 @@
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="P4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="P4" s="1" t="s">
+      <c r="Q4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="R4" s="1"/>
+      <c r="R4" s="1" t="s">
+        <v>256</v>
+      </c>
       <c r="S4" s="1"/>
       <c r="T4" s="1"/>
       <c r="U4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="V4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="V4" s="1" t="s">
+      <c r="W4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="W4" s="1" t="s">
+      <c r="X4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="X4" s="1" t="s">
+      <c r="Y4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="Y4" s="1" t="s">
+      <c r="Z4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="Z4" s="1" t="s">
+      <c r="AA4" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AA4" s="1" t="s">
+      <c r="AB4" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="AB4" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="AC4" s="1"/>
       <c r="AD4" s="1"/>
@@ -1613,7 +1620,7 @@
       </c>
       <c r="R5" s="4">
         <f t="shared" si="0"/>
-        <v>2068.9649039199994</v>
+        <v>4415.19846856</v>
       </c>
       <c r="S5" s="1"/>
       <c r="T5" s="1"/>
@@ -1652,7 +1659,7 @@
       <c r="AC5" s="1"/>
       <c r="AD5" s="4">
         <f>SUM(AD6:AD499)</f>
-        <v>1818.5341039199998</v>
+        <v>3952</v>
       </c>
       <c r="AE5" s="1"/>
       <c r="AF5" s="1"/>
@@ -1676,10 +1683,10 @@
     </row>
     <row r="6" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>34</v>
       </c>
       <c r="C6" s="1">
         <v>476.79300000000001</v>
@@ -1698,7 +1705,7 @@
       </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J6" s="1"/>
       <c r="K6" s="1">
@@ -1750,10 +1757,10 @@
         <v>59.230600000000003</v>
       </c>
       <c r="AC6" s="17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AD6" s="1">
-        <f>G6*R6</f>
+        <f>ROUND(G6*R6,0)</f>
         <v>0</v>
       </c>
       <c r="AE6" s="1"/>
@@ -1778,10 +1785,10 @@
     </row>
     <row r="7" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C7" s="1">
         <v>933.44100000000003</v>
@@ -1800,7 +1807,7 @@
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J7" s="1"/>
       <c r="K7" s="1">
@@ -1857,7 +1864,7 @@
       </c>
       <c r="AC7" s="1"/>
       <c r="AD7" s="1">
-        <f>G7*R7</f>
+        <f t="shared" ref="AD7:AD70" si="6">ROUND(G7*R7,0)</f>
         <v>0</v>
       </c>
       <c r="AE7" s="1"/>
@@ -1882,10 +1889,10 @@
     </row>
     <row r="8" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C8" s="1">
         <v>967.57</v>
@@ -1904,7 +1911,7 @@
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J8" s="1"/>
       <c r="K8" s="1">
@@ -1961,7 +1968,7 @@
       </c>
       <c r="AC8" s="1"/>
       <c r="AD8" s="1">
-        <f>G8*R8</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AE8" s="1"/>
@@ -1986,10 +1993,10 @@
     </row>
     <row r="9" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>41</v>
       </c>
       <c r="C9" s="1">
         <v>72</v>
@@ -2056,11 +2063,11 @@
         <v>0</v>
       </c>
       <c r="AC9" s="9" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AD9" s="1">
-        <f>G9*R9</f>
-        <v>6.4</v>
+        <f t="shared" si="6"/>
+        <v>6</v>
       </c>
       <c r="AE9" s="1"/>
       <c r="AF9" s="1"/>
@@ -2084,10 +2091,10 @@
     </row>
     <row r="10" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C10" s="1">
         <v>302</v>
@@ -2106,7 +2113,7 @@
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J10" s="1"/>
       <c r="K10" s="1">
@@ -2163,7 +2170,7 @@
       </c>
       <c r="AC10" s="1"/>
       <c r="AD10" s="1">
-        <f>G10*R10</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AE10" s="1"/>
@@ -2188,10 +2195,10 @@
     </row>
     <row r="11" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C11" s="1">
         <v>931</v>
@@ -2210,7 +2217,7 @@
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J11" s="1"/>
       <c r="K11" s="1">
@@ -2230,10 +2237,13 @@
         <f t="shared" si="3"/>
         <v>71.8</v>
       </c>
-      <c r="R11" s="5"/>
+      <c r="R11" s="5">
+        <f>$R$1*Q11-P11-O11-F11</f>
+        <v>99.940000000000055</v>
+      </c>
       <c r="S11" s="1">
         <f t="shared" si="4"/>
-        <v>11.90807799442897</v>
+        <v>13.3</v>
       </c>
       <c r="T11" s="1">
         <f t="shared" si="5"/>
@@ -2265,8 +2275,8 @@
       </c>
       <c r="AC11" s="1"/>
       <c r="AD11" s="1">
-        <f>G11*R11</f>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>45</v>
       </c>
       <c r="AE11" s="1"/>
       <c r="AF11" s="1"/>
@@ -2290,10 +2300,10 @@
     </row>
     <row r="12" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C12" s="1">
         <v>172</v>
@@ -2312,7 +2322,7 @@
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J12" s="1"/>
       <c r="K12" s="1">
@@ -2369,7 +2379,7 @@
       </c>
       <c r="AC12" s="1"/>
       <c r="AD12" s="1">
-        <f>G12*R12</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AE12" s="1"/>
@@ -2394,10 +2404,10 @@
     </row>
     <row r="13" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C13" s="1">
         <v>167</v>
@@ -2416,7 +2426,7 @@
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J13" s="1"/>
       <c r="K13" s="1">
@@ -2468,10 +2478,10 @@
         <v>10.4</v>
       </c>
       <c r="AC13" s="10" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AD13" s="1">
-        <f>G13*R13</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AE13" s="1"/>
@@ -2496,10 +2506,10 @@
     </row>
     <row r="14" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C14" s="1">
         <v>429.78800000000001</v>
@@ -2518,7 +2528,7 @@
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J14" s="1"/>
       <c r="K14" s="1">
@@ -2539,12 +2549,12 @@
         <v>85.927999999999997</v>
       </c>
       <c r="R14" s="5">
-        <f t="shared" ref="R7:R16" si="6">11*Q14-P14-O14-F14</f>
-        <v>428.68200000000002</v>
+        <f>$R$1*Q14-P14-O14-F14</f>
+        <v>626.31640000000016</v>
       </c>
       <c r="S14" s="1">
         <f t="shared" si="4"/>
-        <v>10.999999999999998</v>
+        <v>13.3</v>
       </c>
       <c r="T14" s="1">
         <f t="shared" si="5"/>
@@ -2576,8 +2586,8 @@
       </c>
       <c r="AC14" s="1"/>
       <c r="AD14" s="1">
-        <f>G14*R14</f>
-        <v>428.68200000000002</v>
+        <f t="shared" si="6"/>
+        <v>626</v>
       </c>
       <c r="AE14" s="1"/>
       <c r="AF14" s="1"/>
@@ -2601,10 +2611,10 @@
     </row>
     <row r="15" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C15" s="1">
         <v>611.56600000000003</v>
@@ -2623,7 +2633,7 @@
       </c>
       <c r="H15" s="1"/>
       <c r="I15" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J15" s="1"/>
       <c r="K15" s="1">
@@ -2644,12 +2654,12 @@
         <v>341.27480000000003</v>
       </c>
       <c r="R15" s="5">
-        <f t="shared" si="6"/>
-        <v>427.05700000000024</v>
+        <f t="shared" ref="R15" si="7">$R$1*Q15-P15-O15-F15</f>
+        <v>1211.9890400000002</v>
       </c>
       <c r="S15" s="1">
         <f t="shared" si="4"/>
-        <v>11</v>
+        <v>13.3</v>
       </c>
       <c r="T15" s="1">
         <f t="shared" si="5"/>
@@ -2681,8 +2691,8 @@
       </c>
       <c r="AC15" s="1"/>
       <c r="AD15" s="1">
-        <f>G15*R15</f>
-        <v>427.05700000000024</v>
+        <f t="shared" si="6"/>
+        <v>1212</v>
       </c>
       <c r="AE15" s="1"/>
       <c r="AF15" s="1"/>
@@ -2706,10 +2716,10 @@
     </row>
     <row r="16" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C16" s="1">
         <v>43.6</v>
@@ -2728,7 +2738,7 @@
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J16" s="1"/>
       <c r="K16" s="1">
@@ -2783,7 +2793,7 @@
       </c>
       <c r="AC16" s="1"/>
       <c r="AD16" s="1">
-        <f>G16*R16</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AE16" s="1"/>
@@ -2808,10 +2818,10 @@
     </row>
     <row r="17" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C17" s="11">
         <v>-0.28699999999999998</v>
@@ -2826,10 +2836,10 @@
       </c>
       <c r="H17" s="11"/>
       <c r="I17" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="J17" s="11" t="s">
         <v>58</v>
-      </c>
-      <c r="J17" s="11" t="s">
-        <v>59</v>
       </c>
       <c r="K17" s="11">
         <v>60</v>
@@ -2880,9 +2890,12 @@
         <v>325.00940000000003</v>
       </c>
       <c r="AC17" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="AD17" s="11"/>
+        <v>59</v>
+      </c>
+      <c r="AD17" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AE17" s="1"/>
       <c r="AF17" s="1"/>
       <c r="AG17" s="1"/>
@@ -2905,10 +2918,10 @@
     </row>
     <row r="18" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C18" s="1">
         <v>33.787999999999997</v>
@@ -2927,7 +2940,7 @@
       </c>
       <c r="H18" s="1"/>
       <c r="I18" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J18" s="1"/>
       <c r="K18" s="1">
@@ -2984,7 +2997,7 @@
       </c>
       <c r="AC18" s="1"/>
       <c r="AD18" s="1">
-        <f>G18*R18</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AE18" s="1"/>
@@ -3009,10 +3022,10 @@
     </row>
     <row r="19" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C19" s="1">
         <v>39.095999999999997</v>
@@ -3031,7 +3044,7 @@
       </c>
       <c r="H19" s="1"/>
       <c r="I19" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J19" s="1"/>
       <c r="K19" s="1">
@@ -3088,7 +3101,7 @@
       </c>
       <c r="AC19" s="1"/>
       <c r="AD19" s="1">
-        <f>G19*R19</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AE19" s="1"/>
@@ -3113,10 +3126,10 @@
     </row>
     <row r="20" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C20" s="1">
         <v>334.31099999999998</v>
@@ -3135,7 +3148,7 @@
       </c>
       <c r="H20" s="1"/>
       <c r="I20" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J20" s="1"/>
       <c r="K20" s="1">
@@ -3190,7 +3203,7 @@
       </c>
       <c r="AC20" s="1"/>
       <c r="AD20" s="1">
-        <f>G20*R20</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AE20" s="1"/>
@@ -3215,10 +3228,10 @@
     </row>
     <row r="21" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C21" s="1">
         <v>1.3280000000000001</v>
@@ -3237,7 +3250,7 @@
       </c>
       <c r="H21" s="1"/>
       <c r="I21" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J21" s="1"/>
       <c r="K21" s="1">
@@ -3290,7 +3303,7 @@
       </c>
       <c r="AC21" s="1"/>
       <c r="AD21" s="1">
-        <f>G21*R21</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AE21" s="1"/>
@@ -3315,10 +3328,10 @@
     </row>
     <row r="22" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C22" s="1">
         <v>250.464</v>
@@ -3337,7 +3350,7 @@
       </c>
       <c r="H22" s="1"/>
       <c r="I22" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J22" s="1"/>
       <c r="K22" s="1">
@@ -3394,7 +3407,7 @@
       </c>
       <c r="AC22" s="1"/>
       <c r="AD22" s="1">
-        <f>G22*R22</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AE22" s="1"/>
@@ -3419,10 +3432,10 @@
     </row>
     <row r="23" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C23" s="1">
         <v>35.234000000000002</v>
@@ -3441,7 +3454,7 @@
       </c>
       <c r="H23" s="1"/>
       <c r="I23" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J23" s="1"/>
       <c r="K23" s="1">
@@ -3498,7 +3511,7 @@
       </c>
       <c r="AC23" s="1"/>
       <c r="AD23" s="1">
-        <f>G23*R23</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AE23" s="1"/>
@@ -3523,10 +3536,10 @@
     </row>
     <row r="24" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C24" s="1">
         <v>431.11099999999999</v>
@@ -3545,7 +3558,7 @@
       </c>
       <c r="H24" s="1"/>
       <c r="I24" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J24" s="1"/>
       <c r="K24" s="1">
@@ -3602,7 +3615,7 @@
       </c>
       <c r="AC24" s="1"/>
       <c r="AD24" s="1">
-        <f>G24*R24</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AE24" s="1"/>
@@ -3627,10 +3640,10 @@
     </row>
     <row r="25" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C25" s="1">
         <v>34.036999999999999</v>
@@ -3649,7 +3662,7 @@
       </c>
       <c r="H25" s="1"/>
       <c r="I25" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J25" s="1"/>
       <c r="K25" s="1">
@@ -3704,7 +3717,7 @@
       </c>
       <c r="AC25" s="1"/>
       <c r="AD25" s="1">
-        <f>G25*R25</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AE25" s="1"/>
@@ -3729,10 +3742,10 @@
     </row>
     <row r="26" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C26" s="1">
         <v>-20.736000000000001</v>
@@ -3751,7 +3764,7 @@
       </c>
       <c r="H26" s="1"/>
       <c r="I26" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J26" s="1"/>
       <c r="K26" s="1">
@@ -3806,7 +3819,7 @@
       </c>
       <c r="AC26" s="1"/>
       <c r="AD26" s="1">
-        <f>G26*R26</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AE26" s="1"/>
@@ -3831,10 +3844,10 @@
     </row>
     <row r="27" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C27" s="1">
         <v>136.83199999999999</v>
@@ -3853,7 +3866,7 @@
       </c>
       <c r="H27" s="1"/>
       <c r="I27" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J27" s="1"/>
       <c r="K27" s="1">
@@ -3910,7 +3923,7 @@
       </c>
       <c r="AC27" s="1"/>
       <c r="AD27" s="1">
-        <f>G27*R27</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AE27" s="1"/>
@@ -3935,10 +3948,10 @@
     </row>
     <row r="28" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C28" s="1">
         <v>195.179</v>
@@ -3957,7 +3970,7 @@
       </c>
       <c r="H28" s="1"/>
       <c r="I28" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J28" s="1"/>
       <c r="K28" s="1">
@@ -4012,7 +4025,7 @@
       </c>
       <c r="AC28" s="1"/>
       <c r="AD28" s="1">
-        <f>G28*R28</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AE28" s="1"/>
@@ -4037,10 +4050,10 @@
     </row>
     <row r="29" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C29" s="1">
         <v>1.96</v>
@@ -4059,7 +4072,7 @@
       </c>
       <c r="H29" s="1"/>
       <c r="I29" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J29" s="1"/>
       <c r="K29" s="1">
@@ -4114,7 +4127,7 @@
       </c>
       <c r="AC29" s="1"/>
       <c r="AD29" s="1">
-        <f>G29*R29</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AE29" s="1"/>
@@ -4139,10 +4152,10 @@
     </row>
     <row r="30" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C30" s="1">
         <v>-16.491</v>
@@ -4157,7 +4170,7 @@
       </c>
       <c r="H30" s="1"/>
       <c r="I30" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
@@ -4212,7 +4225,7 @@
       </c>
       <c r="AC30" s="1"/>
       <c r="AD30" s="1">
-        <f>G30*R30</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AE30" s="1"/>
@@ -4237,10 +4250,10 @@
     </row>
     <row r="31" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C31" s="1">
         <v>14.065</v>
@@ -4259,7 +4272,7 @@
       </c>
       <c r="H31" s="1"/>
       <c r="I31" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J31" s="1"/>
       <c r="K31" s="1">
@@ -4280,7 +4293,7 @@
         <v>10.4878</v>
       </c>
       <c r="R31" s="5">
-        <f t="shared" ref="R18:R50" si="7">11*Q31-P31-O31-F31</f>
+        <f t="shared" ref="R31" si="8">11*Q31-P31-O31-F31</f>
         <v>27.91271200000002</v>
       </c>
       <c r="S31" s="1">
@@ -4317,8 +4330,8 @@
       </c>
       <c r="AC31" s="1"/>
       <c r="AD31" s="1">
-        <f>G31*R31</f>
-        <v>27.91271200000002</v>
+        <f t="shared" si="6"/>
+        <v>28</v>
       </c>
       <c r="AE31" s="1"/>
       <c r="AF31" s="1"/>
@@ -4342,10 +4355,10 @@
     </row>
     <row r="32" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C32" s="1">
         <v>63.396000000000001</v>
@@ -4364,7 +4377,7 @@
       </c>
       <c r="H32" s="1"/>
       <c r="I32" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J32" s="1"/>
       <c r="K32" s="1">
@@ -4421,7 +4434,7 @@
       </c>
       <c r="AC32" s="1"/>
       <c r="AD32" s="1">
-        <f>G32*R32</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AE32" s="1"/>
@@ -4446,10 +4459,10 @@
     </row>
     <row r="33" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C33" s="1">
         <v>36.04</v>
@@ -4468,7 +4481,7 @@
       </c>
       <c r="H33" s="1"/>
       <c r="I33" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J33" s="1"/>
       <c r="K33" s="1">
@@ -4525,7 +4538,7 @@
       </c>
       <c r="AC33" s="1"/>
       <c r="AD33" s="1">
-        <f>G33*R33</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AE33" s="1"/>
@@ -4550,10 +4563,10 @@
     </row>
     <row r="34" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C34" s="1">
         <v>36.604999999999997</v>
@@ -4572,7 +4585,7 @@
       </c>
       <c r="H34" s="1"/>
       <c r="I34" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J34" s="1"/>
       <c r="K34" s="1">
@@ -4629,7 +4642,7 @@
       </c>
       <c r="AC34" s="1"/>
       <c r="AD34" s="1">
-        <f>G34*R34</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AE34" s="1"/>
@@ -4654,10 +4667,10 @@
     </row>
     <row r="35" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C35" s="1">
         <v>1615</v>
@@ -4676,7 +4689,7 @@
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J35" s="1"/>
       <c r="K35" s="1">
@@ -4733,7 +4746,7 @@
       </c>
       <c r="AC35" s="1"/>
       <c r="AD35" s="1">
-        <f>G35*R35</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AE35" s="1"/>
@@ -4758,10 +4771,10 @@
     </row>
     <row r="36" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C36" s="1">
         <v>301</v>
@@ -4780,7 +4793,7 @@
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J36" s="1"/>
       <c r="K36" s="1">
@@ -4837,7 +4850,7 @@
       </c>
       <c r="AC36" s="1"/>
       <c r="AD36" s="1">
-        <f>G36*R36</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AE36" s="1"/>
@@ -4862,10 +4875,10 @@
     </row>
     <row r="37" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C37" s="1">
         <v>131</v>
@@ -4884,7 +4897,7 @@
       </c>
       <c r="H37" s="1"/>
       <c r="I37" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="J37" s="1"/>
       <c r="K37" s="1">
@@ -4941,7 +4954,7 @@
       </c>
       <c r="AC37" s="1"/>
       <c r="AD37" s="1">
-        <f>G37*R37</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AE37" s="1"/>
@@ -4966,10 +4979,10 @@
     </row>
     <row r="38" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C38" s="1">
         <v>1</v>
@@ -4988,14 +5001,14 @@
       </c>
       <c r="H38" s="1"/>
       <c r="I38" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J38" s="1"/>
       <c r="K38" s="1">
         <v>8</v>
       </c>
       <c r="L38" s="1">
-        <f t="shared" ref="L38:L69" si="8">E38-K38</f>
+        <f t="shared" ref="L38:L69" si="9">E38-K38</f>
         <v>-5</v>
       </c>
       <c r="M38" s="1"/>
@@ -5043,7 +5056,7 @@
       </c>
       <c r="AC38" s="1"/>
       <c r="AD38" s="1">
-        <f>G38*R38</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AE38" s="1"/>
@@ -5068,10 +5081,10 @@
     </row>
     <row r="39" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C39" s="1">
         <v>8.2729999999999997</v>
@@ -5088,14 +5101,14 @@
       </c>
       <c r="H39" s="1"/>
       <c r="I39" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J39" s="1"/>
       <c r="K39" s="1">
         <v>19.399999999999999</v>
       </c>
       <c r="L39" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>-19.399999999999999</v>
       </c>
       <c r="M39" s="1"/>
@@ -5142,10 +5155,10 @@
         <v>2.5695999999999999</v>
       </c>
       <c r="AC39" s="17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AD39" s="1">
-        <f>G39*R39</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AE39" s="1"/>
@@ -5170,10 +5183,10 @@
     </row>
     <row r="40" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C40" s="1">
         <v>359</v>
@@ -5192,14 +5205,14 @@
       </c>
       <c r="H40" s="1"/>
       <c r="I40" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="J40" s="1"/>
       <c r="K40" s="1">
         <v>252</v>
       </c>
       <c r="L40" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>102</v>
       </c>
       <c r="M40" s="1"/>
@@ -5214,10 +5227,13 @@
         <f t="shared" si="3"/>
         <v>70.8</v>
       </c>
-      <c r="R40" s="5"/>
+      <c r="R40" s="5">
+        <f>$R$1*Q40-P40-O40-F40</f>
+        <v>30.440000000000055</v>
+      </c>
       <c r="S40" s="1">
         <f t="shared" si="4"/>
-        <v>12.87005649717514</v>
+        <v>13.3</v>
       </c>
       <c r="T40" s="1">
         <f t="shared" si="5"/>
@@ -5249,8 +5265,8 @@
       </c>
       <c r="AC40" s="1"/>
       <c r="AD40" s="1">
-        <f>G40*R40</f>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>3</v>
       </c>
       <c r="AE40" s="1"/>
       <c r="AF40" s="1"/>
@@ -5274,10 +5290,10 @@
     </row>
     <row r="41" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C41" s="1">
         <v>242</v>
@@ -5296,14 +5312,14 @@
       </c>
       <c r="H41" s="1"/>
       <c r="I41" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J41" s="1"/>
       <c r="K41" s="1">
         <v>179</v>
       </c>
       <c r="L41" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>-27</v>
       </c>
       <c r="M41" s="1"/>
@@ -5353,7 +5369,7 @@
       </c>
       <c r="AC41" s="1"/>
       <c r="AD41" s="1">
-        <f>G41*R41</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AE41" s="1"/>
@@ -5378,10 +5394,10 @@
     </row>
     <row r="42" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C42" s="1">
         <v>106.345</v>
@@ -5400,14 +5416,14 @@
       </c>
       <c r="H42" s="1"/>
       <c r="I42" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="J42" s="1"/>
       <c r="K42" s="1">
         <v>71.099999999999994</v>
       </c>
       <c r="L42" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>-14.555999999999997</v>
       </c>
       <c r="M42" s="1"/>
@@ -5457,7 +5473,7 @@
       </c>
       <c r="AC42" s="1"/>
       <c r="AD42" s="1">
-        <f>G42*R42</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AE42" s="1"/>
@@ -5482,10 +5498,10 @@
     </row>
     <row r="43" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C43" s="1">
         <v>120</v>
@@ -5504,14 +5520,14 @@
       </c>
       <c r="H43" s="1"/>
       <c r="I43" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J43" s="1"/>
       <c r="K43" s="1">
         <v>103</v>
       </c>
       <c r="L43" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>-19</v>
       </c>
       <c r="M43" s="1"/>
@@ -5561,7 +5577,7 @@
       </c>
       <c r="AC43" s="1"/>
       <c r="AD43" s="1">
-        <f>G43*R43</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AE43" s="1"/>
@@ -5586,10 +5602,10 @@
     </row>
     <row r="44" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C44" s="1">
         <v>137</v>
@@ -5608,14 +5624,14 @@
       </c>
       <c r="H44" s="1"/>
       <c r="I44" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J44" s="1"/>
       <c r="K44" s="1">
         <v>117</v>
       </c>
       <c r="L44" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>-10</v>
       </c>
       <c r="M44" s="1"/>
@@ -5661,7 +5677,7 @@
       </c>
       <c r="AC44" s="1"/>
       <c r="AD44" s="1">
-        <f>G44*R44</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AE44" s="1"/>
@@ -5686,10 +5702,10 @@
     </row>
     <row r="45" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C45" s="1">
         <v>48.343000000000004</v>
@@ -5708,14 +5724,14 @@
       </c>
       <c r="H45" s="1"/>
       <c r="I45" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J45" s="1"/>
       <c r="K45" s="1">
         <v>68.2</v>
       </c>
       <c r="L45" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>-13.11</v>
       </c>
       <c r="M45" s="1"/>
@@ -5765,7 +5781,7 @@
       </c>
       <c r="AC45" s="1"/>
       <c r="AD45" s="1">
-        <f>G45*R45</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AE45" s="1"/>
@@ -5790,10 +5806,10 @@
     </row>
     <row r="46" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C46" s="1">
         <v>125.739</v>
@@ -5812,14 +5828,14 @@
       </c>
       <c r="H46" s="1"/>
       <c r="I46" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J46" s="1"/>
       <c r="K46" s="1">
         <v>112.5</v>
       </c>
       <c r="L46" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>-18.060000000000002</v>
       </c>
       <c r="M46" s="1"/>
@@ -5869,7 +5885,7 @@
       </c>
       <c r="AC46" s="1"/>
       <c r="AD46" s="1">
-        <f>G46*R46</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AE46" s="1"/>
@@ -5894,10 +5910,10 @@
     </row>
     <row r="47" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C47" s="1">
         <v>634</v>
@@ -5916,14 +5932,14 @@
       </c>
       <c r="H47" s="1"/>
       <c r="I47" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J47" s="1"/>
       <c r="K47" s="1">
         <v>360</v>
       </c>
       <c r="L47" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>-1</v>
       </c>
       <c r="M47" s="1"/>
@@ -5938,10 +5954,13 @@
         <f t="shared" si="3"/>
         <v>71.8</v>
       </c>
-      <c r="R47" s="5"/>
+      <c r="R47" s="5">
+        <f t="shared" ref="R47:R48" si="10">$R$1*Q47-P47-O47-F47</f>
+        <v>109.53999999999996</v>
+      </c>
       <c r="S47" s="1">
         <f t="shared" si="4"/>
-        <v>11.774373259052927</v>
+        <v>13.3</v>
       </c>
       <c r="T47" s="1">
         <f t="shared" si="5"/>
@@ -5973,8 +5992,8 @@
       </c>
       <c r="AC47" s="1"/>
       <c r="AD47" s="1">
-        <f>G47*R47</f>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>38</v>
       </c>
       <c r="AE47" s="1"/>
       <c r="AF47" s="1"/>
@@ -5998,10 +6017,10 @@
     </row>
     <row r="48" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C48" s="1">
         <v>98</v>
@@ -6020,14 +6039,14 @@
       </c>
       <c r="H48" s="1"/>
       <c r="I48" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J48" s="1"/>
       <c r="K48" s="1">
         <v>303</v>
       </c>
       <c r="L48" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>-93</v>
       </c>
       <c r="M48" s="1"/>
@@ -6039,12 +6058,12 @@
         <v>42</v>
       </c>
       <c r="R48" s="5">
-        <f t="shared" si="7"/>
-        <v>28</v>
+        <f t="shared" si="10"/>
+        <v>124.60000000000002</v>
       </c>
       <c r="S48" s="1">
         <f t="shared" si="4"/>
-        <v>11</v>
+        <v>13.3</v>
       </c>
       <c r="T48" s="1">
         <f t="shared" si="5"/>
@@ -6076,8 +6095,8 @@
       </c>
       <c r="AC48" s="1"/>
       <c r="AD48" s="1">
-        <f>G48*R48</f>
-        <v>11.200000000000001</v>
+        <f t="shared" si="6"/>
+        <v>50</v>
       </c>
       <c r="AE48" s="1"/>
       <c r="AF48" s="1"/>
@@ -6101,10 +6120,10 @@
     </row>
     <row r="49" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C49" s="1">
         <v>1.3560000000000001</v>
@@ -6123,14 +6142,14 @@
       </c>
       <c r="H49" s="1"/>
       <c r="I49" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J49" s="1"/>
       <c r="K49" s="1">
         <v>18.899999999999999</v>
       </c>
       <c r="L49" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>-5.4389999999999983</v>
       </c>
       <c r="M49" s="1"/>
@@ -6178,7 +6197,7 @@
       </c>
       <c r="AC49" s="1"/>
       <c r="AD49" s="1">
-        <f>G49*R49</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AE49" s="1"/>
@@ -6203,10 +6222,10 @@
     </row>
     <row r="50" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C50" s="1">
         <v>163.75200000000001</v>
@@ -6225,14 +6244,14 @@
       </c>
       <c r="H50" s="1"/>
       <c r="I50" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J50" s="1"/>
       <c r="K50" s="1">
         <v>83.15</v>
       </c>
       <c r="L50" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4.2749999999999915</v>
       </c>
       <c r="M50" s="1"/>
@@ -6282,7 +6301,7 @@
       </c>
       <c r="AC50" s="1"/>
       <c r="AD50" s="1">
-        <f>G50*R50</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AE50" s="1"/>
@@ -6307,10 +6326,10 @@
     </row>
     <row r="51" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A51" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C51" s="11">
         <v>-4.0000000000000001E-3</v>
@@ -6327,12 +6346,12 @@
       </c>
       <c r="H51" s="11"/>
       <c r="I51" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="J51" s="11"/>
       <c r="K51" s="11"/>
       <c r="L51" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>-0.81399999999999995</v>
       </c>
       <c r="M51" s="11"/>
@@ -6377,7 +6396,10 @@
         <v>1.4636</v>
       </c>
       <c r="AC51" s="11"/>
-      <c r="AD51" s="11"/>
+      <c r="AD51" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AE51" s="1"/>
       <c r="AF51" s="1"/>
       <c r="AG51" s="1"/>
@@ -6400,10 +6422,10 @@
     </row>
     <row r="52" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C52" s="1">
         <v>-0.39500000000000002</v>
@@ -6420,14 +6442,14 @@
       </c>
       <c r="H52" s="1"/>
       <c r="I52" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J52" s="1"/>
       <c r="K52" s="1">
         <v>22</v>
       </c>
       <c r="L52" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>-22</v>
       </c>
       <c r="M52" s="1"/>
@@ -6473,7 +6495,7 @@
       </c>
       <c r="AC52" s="1"/>
       <c r="AD52" s="1">
-        <f>G52*R52</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AE52" s="1"/>
@@ -6498,10 +6520,10 @@
     </row>
     <row r="53" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C53" s="1">
         <v>146</v>
@@ -6520,14 +6542,14 @@
       </c>
       <c r="H53" s="1"/>
       <c r="I53" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J53" s="1"/>
       <c r="K53" s="1">
         <v>115</v>
       </c>
       <c r="L53" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>-11</v>
       </c>
       <c r="M53" s="1"/>
@@ -6573,7 +6595,7 @@
       </c>
       <c r="AC53" s="1"/>
       <c r="AD53" s="1">
-        <f>G53*R53</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AE53" s="1"/>
@@ -6598,10 +6620,10 @@
     </row>
     <row r="54" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C54" s="1">
         <v>259</v>
@@ -6620,14 +6642,14 @@
       </c>
       <c r="H54" s="1"/>
       <c r="I54" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J54" s="1"/>
       <c r="K54" s="1">
         <v>179</v>
       </c>
       <c r="L54" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>-1</v>
       </c>
       <c r="M54" s="1"/>
@@ -6677,7 +6699,7 @@
       </c>
       <c r="AC54" s="1"/>
       <c r="AD54" s="1">
-        <f>G54*R54</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AE54" s="1"/>
@@ -6702,10 +6724,10 @@
     </row>
     <row r="55" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C55" s="1">
         <v>5</v>
@@ -6724,14 +6746,14 @@
       </c>
       <c r="H55" s="1"/>
       <c r="I55" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J55" s="1"/>
       <c r="K55" s="1">
         <v>42</v>
       </c>
       <c r="L55" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>-36</v>
       </c>
       <c r="M55" s="1"/>
@@ -6779,7 +6801,7 @@
       </c>
       <c r="AC55" s="1"/>
       <c r="AD55" s="1">
-        <f>G55*R55</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AE55" s="1"/>
@@ -6804,10 +6826,10 @@
     </row>
     <row r="56" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C56" s="1">
         <v>52</v>
@@ -6826,14 +6848,14 @@
       </c>
       <c r="H56" s="1"/>
       <c r="I56" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J56" s="1"/>
       <c r="K56" s="1">
         <v>98</v>
       </c>
       <c r="L56" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>-27</v>
       </c>
       <c r="M56" s="1"/>
@@ -6884,8 +6906,8 @@
       </c>
       <c r="AC56" s="1"/>
       <c r="AD56" s="1">
-        <f>G56*R56</f>
-        <v>35.347200000000001</v>
+        <f t="shared" si="6"/>
+        <v>35</v>
       </c>
       <c r="AE56" s="1"/>
       <c r="AF56" s="1"/>
@@ -6909,10 +6931,10 @@
     </row>
     <row r="57" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C57" s="1">
         <v>102.64100000000001</v>
@@ -6931,14 +6953,14 @@
       </c>
       <c r="H57" s="1"/>
       <c r="I57" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J57" s="1"/>
       <c r="K57" s="1">
         <v>110.55</v>
       </c>
       <c r="L57" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>6.8239999999999981</v>
       </c>
       <c r="M57" s="1"/>
@@ -6988,7 +7010,7 @@
       </c>
       <c r="AC57" s="1"/>
       <c r="AD57" s="1">
-        <f>G57*R57</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AE57" s="1"/>
@@ -7013,10 +7035,10 @@
     </row>
     <row r="58" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C58" s="1">
         <v>1</v>
@@ -7035,14 +7057,14 @@
       </c>
       <c r="H58" s="1"/>
       <c r="I58" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J58" s="1"/>
       <c r="K58" s="1">
         <v>99</v>
       </c>
       <c r="L58" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>11</v>
       </c>
       <c r="M58" s="1"/>
@@ -7090,7 +7112,7 @@
       </c>
       <c r="AC58" s="1"/>
       <c r="AD58" s="1">
-        <f>G58*R58</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AE58" s="1"/>
@@ -7115,10 +7137,10 @@
     </row>
     <row r="59" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C59" s="1">
         <v>44.151000000000003</v>
@@ -7137,14 +7159,14 @@
       </c>
       <c r="H59" s="1"/>
       <c r="I59" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="J59" s="1"/>
       <c r="K59" s="1">
         <v>69.25</v>
       </c>
       <c r="L59" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>11.623999999999995</v>
       </c>
       <c r="M59" s="1"/>
@@ -7192,7 +7214,7 @@
       </c>
       <c r="AC59" s="1"/>
       <c r="AD59" s="1">
-        <f>G59*R59</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AE59" s="1"/>
@@ -7217,10 +7239,10 @@
     </row>
     <row r="60" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C60" s="1">
         <v>5.5E-2</v>
@@ -7239,14 +7261,14 @@
       </c>
       <c r="H60" s="1"/>
       <c r="I60" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J60" s="1"/>
       <c r="K60" s="1">
         <v>14</v>
       </c>
       <c r="L60" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>-0.4740000000000002</v>
       </c>
       <c r="M60" s="1"/>
@@ -7294,7 +7316,7 @@
       </c>
       <c r="AC60" s="1"/>
       <c r="AD60" s="1">
-        <f>G60*R60</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AE60" s="1"/>
@@ -7319,10 +7341,10 @@
     </row>
     <row r="61" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C61" s="1">
         <v>126</v>
@@ -7341,14 +7363,14 @@
       </c>
       <c r="H61" s="1"/>
       <c r="I61" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J61" s="1"/>
       <c r="K61" s="1">
         <v>118</v>
       </c>
       <c r="L61" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>45</v>
       </c>
       <c r="M61" s="1"/>
@@ -7398,7 +7420,7 @@
       </c>
       <c r="AC61" s="1"/>
       <c r="AD61" s="1">
-        <f>G61*R61</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AE61" s="1"/>
@@ -7423,10 +7445,10 @@
     </row>
     <row r="62" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C62" s="1">
         <v>19</v>
@@ -7445,14 +7467,14 @@
       </c>
       <c r="H62" s="1"/>
       <c r="I62" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J62" s="1"/>
       <c r="K62" s="1">
         <v>29</v>
       </c>
       <c r="L62" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>-11</v>
       </c>
       <c r="M62" s="1"/>
@@ -7498,7 +7520,7 @@
       </c>
       <c r="AC62" s="1"/>
       <c r="AD62" s="1">
-        <f>G62*R62</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AE62" s="1"/>
@@ -7523,10 +7545,10 @@
     </row>
     <row r="63" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C63" s="1">
         <v>0.41699999999999998</v>
@@ -7543,14 +7565,14 @@
       </c>
       <c r="H63" s="1"/>
       <c r="I63" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J63" s="1"/>
       <c r="K63" s="1">
         <v>12.8</v>
       </c>
       <c r="L63" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>-12.8</v>
       </c>
       <c r="M63" s="1"/>
@@ -7598,7 +7620,7 @@
       </c>
       <c r="AC63" s="1"/>
       <c r="AD63" s="1">
-        <f>G63*R63</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AE63" s="1"/>
@@ -7623,10 +7645,10 @@
     </row>
     <row r="64" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C64" s="1">
         <v>2.2770000000000001</v>
@@ -7645,14 +7667,14 @@
       </c>
       <c r="H64" s="1"/>
       <c r="I64" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J64" s="1"/>
       <c r="K64" s="1">
         <v>28.5</v>
       </c>
       <c r="L64" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>-4.1859999999999999</v>
       </c>
       <c r="M64" s="1"/>
@@ -7698,7 +7720,7 @@
       </c>
       <c r="AC64" s="1"/>
       <c r="AD64" s="1">
-        <f>G64*R64</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AE64" s="1"/>
@@ -7723,10 +7745,10 @@
     </row>
     <row r="65" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C65" s="1">
         <v>659</v>
@@ -7745,14 +7767,14 @@
       </c>
       <c r="H65" s="1"/>
       <c r="I65" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J65" s="1"/>
       <c r="K65" s="1">
         <v>364</v>
       </c>
       <c r="L65" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>-6</v>
       </c>
       <c r="M65" s="1"/>
@@ -7802,7 +7824,7 @@
       </c>
       <c r="AC65" s="1"/>
       <c r="AD65" s="1">
-        <f>G65*R65</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AE65" s="1"/>
@@ -7827,10 +7849,10 @@
     </row>
     <row r="66" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C66" s="1">
         <v>147</v>
@@ -7849,14 +7871,14 @@
       </c>
       <c r="H66" s="1"/>
       <c r="I66" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J66" s="1"/>
       <c r="K66" s="1">
         <v>249</v>
       </c>
       <c r="L66" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>-62</v>
       </c>
       <c r="M66" s="1"/>
@@ -7904,7 +7926,7 @@
       </c>
       <c r="AC66" s="1"/>
       <c r="AD66" s="1">
-        <f>G66*R66</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AE66" s="1"/>
@@ -7929,10 +7951,10 @@
     </row>
     <row r="67" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C67" s="1">
         <v>3.2839999999999998</v>
@@ -7951,14 +7973,14 @@
       </c>
       <c r="H67" s="1"/>
       <c r="I67" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J67" s="1"/>
       <c r="K67" s="1">
         <v>110.8</v>
       </c>
       <c r="L67" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>-32.105000000000004</v>
       </c>
       <c r="M67" s="1"/>
@@ -8004,7 +8026,7 @@
       </c>
       <c r="AC67" s="1"/>
       <c r="AD67" s="1">
-        <f>G67*R67</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AE67" s="1"/>
@@ -8029,10 +8051,10 @@
     </row>
     <row r="68" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C68" s="1">
         <v>-0.437</v>
@@ -8051,14 +8073,14 @@
       </c>
       <c r="H68" s="1"/>
       <c r="I68" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J68" s="1"/>
       <c r="K68" s="1">
         <v>74</v>
       </c>
       <c r="L68" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>-14.594999999999999</v>
       </c>
       <c r="M68" s="1"/>
@@ -8106,7 +8128,7 @@
       </c>
       <c r="AC68" s="1"/>
       <c r="AD68" s="1">
-        <f>G68*R68</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AE68" s="1"/>
@@ -8131,10 +8153,10 @@
     </row>
     <row r="69" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C69" s="1">
         <v>329.45600000000002</v>
@@ -8153,14 +8175,14 @@
       </c>
       <c r="H69" s="1"/>
       <c r="I69" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J69" s="1"/>
       <c r="K69" s="1">
         <v>341.8</v>
       </c>
       <c r="L69" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>25.58499999999998</v>
       </c>
       <c r="M69" s="1"/>
@@ -8210,7 +8232,7 @@
       </c>
       <c r="AC69" s="1"/>
       <c r="AD69" s="1">
-        <f>G69*R69</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AE69" s="1"/>
@@ -8235,10 +8257,10 @@
     </row>
     <row r="70" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C70" s="1">
         <v>3.2269999999999999</v>
@@ -8257,14 +8279,14 @@
       </c>
       <c r="H70" s="1"/>
       <c r="I70" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J70" s="1"/>
       <c r="K70" s="1">
         <v>108.1</v>
       </c>
       <c r="L70" s="1">
-        <f t="shared" ref="L70:L101" si="9">E70-K70</f>
+        <f t="shared" ref="L70:L101" si="11">E70-K70</f>
         <v>-29.963999999999999</v>
       </c>
       <c r="M70" s="1"/>
@@ -8312,7 +8334,7 @@
       </c>
       <c r="AC70" s="1"/>
       <c r="AD70" s="1">
-        <f>G70*R70</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AE70" s="1"/>
@@ -8337,10 +8359,10 @@
     </row>
     <row r="71" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C71" s="1">
         <v>25</v>
@@ -8359,14 +8381,14 @@
       </c>
       <c r="H71" s="1"/>
       <c r="I71" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J71" s="1"/>
       <c r="K71" s="1">
         <v>10</v>
       </c>
       <c r="L71" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>-1</v>
       </c>
       <c r="M71" s="1"/>
@@ -8376,16 +8398,16 @@
         <v>18.599999999999991</v>
       </c>
       <c r="Q71" s="1">
-        <f t="shared" ref="Q71:Q114" si="10">E71/5</f>
+        <f t="shared" ref="Q71:Q114" si="12">E71/5</f>
         <v>1.8</v>
       </c>
       <c r="R71" s="5"/>
       <c r="S71" s="1">
-        <f t="shared" ref="S71:S114" si="11">(F71+O71+P71+R71)/Q71</f>
+        <f t="shared" ref="S71:S114" si="13">(F71+O71+P71+R71)/Q71</f>
         <v>25.888888888888886</v>
       </c>
       <c r="T71" s="1">
-        <f t="shared" ref="T71:T114" si="12">(F71+O71+P71)/Q71</f>
+        <f t="shared" ref="T71:T114" si="14">(F71+O71+P71)/Q71</f>
         <v>25.888888888888886</v>
       </c>
       <c r="U71" s="1">
@@ -8414,7 +8436,7 @@
       </c>
       <c r="AC71" s="1"/>
       <c r="AD71" s="1">
-        <f>G71*R71</f>
+        <f t="shared" ref="AD71:AD114" si="15">ROUND(G71*R71,0)</f>
         <v>0</v>
       </c>
       <c r="AE71" s="1"/>
@@ -8439,10 +8461,10 @@
     </row>
     <row r="72" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C72" s="1">
         <v>366.47300000000001</v>
@@ -8461,14 +8483,14 @@
       </c>
       <c r="H72" s="1"/>
       <c r="I72" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J72" s="1"/>
       <c r="K72" s="1">
         <v>440.15</v>
       </c>
       <c r="L72" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>-14.383999999999958</v>
       </c>
       <c r="M72" s="1"/>
@@ -8478,19 +8500,19 @@
         <v>265.12380000000002</v>
       </c>
       <c r="Q72" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>85.153199999999998</v>
       </c>
       <c r="R72" s="5">
-        <f t="shared" ref="R52:R94" si="13">11*Q72-P72-O72-F72</f>
-        <v>502.91340000000002</v>
+        <f>$R$1*Q72-P72-O72-F72-Q72</f>
+        <v>613.61255999999992</v>
       </c>
       <c r="S72" s="1">
-        <f t="shared" si="11"/>
-        <v>11</v>
+        <f t="shared" si="13"/>
+        <v>12.3</v>
       </c>
       <c r="T72" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>5.0940164315609984</v>
       </c>
       <c r="U72" s="1">
@@ -8519,8 +8541,8 @@
       </c>
       <c r="AC72" s="1"/>
       <c r="AD72" s="1">
-        <f>G72*R72</f>
-        <v>502.91340000000002</v>
+        <f t="shared" si="15"/>
+        <v>614</v>
       </c>
       <c r="AE72" s="1"/>
       <c r="AF72" s="1"/>
@@ -8544,10 +8566,10 @@
     </row>
     <row r="73" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C73" s="1">
         <v>20</v>
@@ -8566,14 +8588,14 @@
       </c>
       <c r="H73" s="1"/>
       <c r="I73" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J73" s="1"/>
       <c r="K73" s="1">
         <v>41</v>
       </c>
       <c r="L73" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>-22</v>
       </c>
       <c r="M73" s="1"/>
@@ -8583,16 +8605,16 @@
       </c>
       <c r="P73" s="1"/>
       <c r="Q73" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>3.8</v>
       </c>
       <c r="R73" s="5"/>
       <c r="S73" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>50.11578947368421</v>
       </c>
       <c r="T73" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>50.11578947368421</v>
       </c>
       <c r="U73" s="1">
@@ -8621,7 +8643,7 @@
       </c>
       <c r="AC73" s="1"/>
       <c r="AD73" s="1">
-        <f>G73*R73</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AE73" s="1"/>
@@ -8646,10 +8668,10 @@
     </row>
     <row r="74" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C74" s="1">
         <v>247</v>
@@ -8668,14 +8690,14 @@
       </c>
       <c r="H74" s="1"/>
       <c r="I74" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J74" s="1"/>
       <c r="K74" s="1">
         <v>99</v>
       </c>
       <c r="L74" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>-1</v>
       </c>
       <c r="M74" s="1"/>
@@ -8687,16 +8709,16 @@
         <v>120.2</v>
       </c>
       <c r="Q74" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>19.600000000000001</v>
       </c>
       <c r="R74" s="5"/>
       <c r="S74" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>17.77551020408163</v>
       </c>
       <c r="T74" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>17.77551020408163</v>
       </c>
       <c r="U74" s="1">
@@ -8725,7 +8747,7 @@
       </c>
       <c r="AC74" s="1"/>
       <c r="AD74" s="1">
-        <f>G74*R74</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AE74" s="1"/>
@@ -8750,10 +8772,10 @@
     </row>
     <row r="75" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C75" s="1">
         <v>187</v>
@@ -8772,14 +8794,14 @@
       </c>
       <c r="H75" s="1"/>
       <c r="I75" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J75" s="1"/>
       <c r="K75" s="1">
         <v>153</v>
       </c>
       <c r="L75" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="M75" s="1"/>
@@ -8791,16 +8813,16 @@
         <v>165.96</v>
       </c>
       <c r="Q75" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>30.8</v>
       </c>
       <c r="R75" s="5"/>
       <c r="S75" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>13.935064935064936</v>
       </c>
       <c r="T75" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>13.935064935064936</v>
       </c>
       <c r="U75" s="1">
@@ -8829,7 +8851,7 @@
       </c>
       <c r="AC75" s="1"/>
       <c r="AD75" s="1">
-        <f>G75*R75</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AE75" s="1"/>
@@ -8854,10 +8876,10 @@
     </row>
     <row r="76" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C76" s="1">
         <v>186</v>
@@ -8876,14 +8898,14 @@
       </c>
       <c r="H76" s="1"/>
       <c r="I76" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J76" s="1"/>
       <c r="K76" s="1">
         <v>103</v>
       </c>
       <c r="L76" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>-12</v>
       </c>
       <c r="M76" s="1"/>
@@ -8893,19 +8915,19 @@
         <v>79</v>
       </c>
       <c r="Q76" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>18.2</v>
       </c>
       <c r="R76" s="5">
+        <f t="shared" ref="R76:R79" si="16">11*Q76-P76-O76-F76</f>
+        <v>26.199999999999989</v>
+      </c>
+      <c r="S76" s="1">
         <f t="shared" si="13"/>
-        <v>26.199999999999989</v>
-      </c>
-      <c r="S76" s="1">
-        <f t="shared" si="11"/>
         <v>11</v>
       </c>
       <c r="T76" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>9.5604395604395602</v>
       </c>
       <c r="U76" s="1">
@@ -8934,8 +8956,8 @@
       </c>
       <c r="AC76" s="1"/>
       <c r="AD76" s="1">
-        <f>G76*R76</f>
-        <v>9.1699999999999946</v>
+        <f t="shared" si="15"/>
+        <v>9</v>
       </c>
       <c r="AE76" s="1"/>
       <c r="AF76" s="1"/>
@@ -8959,10 +8981,10 @@
     </row>
     <row r="77" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C77" s="1">
         <v>-37</v>
@@ -8981,14 +9003,14 @@
       </c>
       <c r="H77" s="1"/>
       <c r="I77" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J77" s="1"/>
       <c r="K77" s="1">
         <v>122</v>
       </c>
       <c r="L77" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>-31</v>
       </c>
       <c r="M77" s="1"/>
@@ -8998,16 +9020,16 @@
       </c>
       <c r="P77" s="1"/>
       <c r="Q77" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>18.2</v>
       </c>
       <c r="R77" s="5"/>
       <c r="S77" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>32.147384615384617</v>
       </c>
       <c r="T77" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>32.147384615384617</v>
       </c>
       <c r="U77" s="1">
@@ -9036,7 +9058,7 @@
       </c>
       <c r="AC77" s="1"/>
       <c r="AD77" s="1">
-        <f>G77*R77</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AE77" s="1"/>
@@ -9061,10 +9083,10 @@
     </row>
     <row r="78" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C78" s="1">
         <v>5</v>
@@ -9083,14 +9105,14 @@
       </c>
       <c r="H78" s="1"/>
       <c r="I78" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J78" s="1"/>
       <c r="K78" s="1">
         <v>9</v>
       </c>
       <c r="L78" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>-5</v>
       </c>
       <c r="M78" s="1"/>
@@ -9100,16 +9122,16 @@
       </c>
       <c r="P78" s="1"/>
       <c r="Q78" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.8</v>
       </c>
       <c r="R78" s="5"/>
       <c r="S78" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>187.29999999999995</v>
       </c>
       <c r="T78" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>187.29999999999995</v>
       </c>
       <c r="U78" s="1">
@@ -9138,7 +9160,7 @@
       </c>
       <c r="AC78" s="1"/>
       <c r="AD78" s="1">
-        <f>G78*R78</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AE78" s="1"/>
@@ -9163,10 +9185,10 @@
     </row>
     <row r="79" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C79" s="1">
         <v>199</v>
@@ -9185,14 +9207,14 @@
       </c>
       <c r="H79" s="1"/>
       <c r="I79" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="J79" s="1"/>
       <c r="K79" s="1">
         <v>111</v>
       </c>
       <c r="L79" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
       <c r="M79" s="1"/>
@@ -9202,19 +9224,19 @@
         <v>109</v>
       </c>
       <c r="Q79" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>22.6</v>
       </c>
       <c r="R79" s="5">
+        <f t="shared" si="16"/>
+        <v>117.60000000000002</v>
+      </c>
+      <c r="S79" s="1">
         <f t="shared" si="13"/>
-        <v>117.60000000000002</v>
-      </c>
-      <c r="S79" s="1">
-        <f t="shared" si="11"/>
         <v>11</v>
       </c>
       <c r="T79" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>5.7964601769911503</v>
       </c>
       <c r="U79" s="1">
@@ -9243,8 +9265,8 @@
       </c>
       <c r="AC79" s="1"/>
       <c r="AD79" s="1">
-        <f>G79*R79</f>
-        <v>47.040000000000013</v>
+        <f t="shared" si="15"/>
+        <v>47</v>
       </c>
       <c r="AE79" s="1"/>
       <c r="AF79" s="1"/>
@@ -9268,10 +9290,10 @@
     </row>
     <row r="80" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C80" s="1">
         <v>10</v>
@@ -9290,14 +9312,14 @@
       </c>
       <c r="H80" s="1"/>
       <c r="I80" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="J80" s="1"/>
       <c r="K80" s="1">
         <v>34</v>
       </c>
       <c r="L80" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>-3</v>
       </c>
       <c r="M80" s="1"/>
@@ -9305,7 +9327,7 @@
       <c r="O80" s="1"/>
       <c r="P80" s="1"/>
       <c r="Q80" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>6.2</v>
       </c>
       <c r="R80" s="5">
@@ -9313,11 +9335,11 @@
         <v>34.800000000000004</v>
       </c>
       <c r="S80" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>9</v>
       </c>
       <c r="T80" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>3.3870967741935485</v>
       </c>
       <c r="U80" s="1">
@@ -9346,8 +9368,8 @@
       </c>
       <c r="AC80" s="1"/>
       <c r="AD80" s="1">
-        <f>G80*R80</f>
-        <v>12.180000000000001</v>
+        <f t="shared" si="15"/>
+        <v>12</v>
       </c>
       <c r="AE80" s="1"/>
       <c r="AF80" s="1"/>
@@ -9371,10 +9393,10 @@
     </row>
     <row r="81" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C81" s="1">
         <v>-4</v>
@@ -9393,14 +9415,14 @@
       </c>
       <c r="H81" s="1"/>
       <c r="I81" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J81" s="1"/>
       <c r="K81" s="1">
         <v>4</v>
       </c>
       <c r="L81" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
       <c r="M81" s="1"/>
@@ -9408,16 +9430,16 @@
       <c r="O81" s="1"/>
       <c r="P81" s="1"/>
       <c r="Q81" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>1.2</v>
       </c>
       <c r="R81" s="5"/>
       <c r="S81" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>111.66666666666667</v>
       </c>
       <c r="T81" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>111.66666666666667</v>
       </c>
       <c r="U81" s="1">
@@ -9446,7 +9468,7 @@
       </c>
       <c r="AC81" s="1"/>
       <c r="AD81" s="1">
-        <f>G81*R81</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AE81" s="1"/>
@@ -9471,10 +9493,10 @@
     </row>
     <row r="82" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C82" s="1">
         <v>77</v>
@@ -9493,14 +9515,14 @@
       </c>
       <c r="H82" s="1"/>
       <c r="I82" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="J82" s="1"/>
       <c r="K82" s="1">
         <v>87</v>
       </c>
       <c r="L82" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>-15</v>
       </c>
       <c r="M82" s="1"/>
@@ -9510,18 +9532,18 @@
         <v>84</v>
       </c>
       <c r="Q82" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>14.4</v>
       </c>
       <c r="R82" s="5">
         <v>8</v>
       </c>
       <c r="S82" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>11.388888888888889</v>
       </c>
       <c r="T82" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>10.833333333333334</v>
       </c>
       <c r="U82" s="1">
@@ -9550,8 +9572,8 @@
       </c>
       <c r="AC82" s="1"/>
       <c r="AD82" s="1">
-        <f>G82*R82</f>
-        <v>3.2</v>
+        <f t="shared" si="15"/>
+        <v>3</v>
       </c>
       <c r="AE82" s="1"/>
       <c r="AF82" s="1"/>
@@ -9575,10 +9597,10 @@
     </row>
     <row r="83" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C83" s="1">
         <v>4.173</v>
@@ -9597,14 +9619,14 @@
       </c>
       <c r="H83" s="1"/>
       <c r="I83" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J83" s="1"/>
       <c r="K83" s="1">
         <v>6.4</v>
       </c>
       <c r="L83" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>-4.9540000000000006</v>
       </c>
       <c r="M83" s="1"/>
@@ -9614,16 +9636,16 @@
       </c>
       <c r="P83" s="1"/>
       <c r="Q83" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.28920000000000001</v>
       </c>
       <c r="R83" s="5"/>
       <c r="S83" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>129.34218533886585</v>
       </c>
       <c r="T83" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>129.34218533886585</v>
       </c>
       <c r="U83" s="1">
@@ -9652,7 +9674,7 @@
       </c>
       <c r="AC83" s="1"/>
       <c r="AD83" s="1">
-        <f>G83*R83</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AE83" s="1"/>
@@ -9677,10 +9699,10 @@
     </row>
     <row r="84" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C84" s="1">
         <v>52.658000000000001</v>
@@ -9699,14 +9721,14 @@
       </c>
       <c r="H84" s="1"/>
       <c r="I84" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="J84" s="1"/>
       <c r="K84" s="1">
         <v>201.36</v>
       </c>
       <c r="L84" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>-34.900000000000006</v>
       </c>
       <c r="M84" s="1"/>
@@ -9716,16 +9738,16 @@
       </c>
       <c r="P84" s="1"/>
       <c r="Q84" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>33.292000000000002</v>
       </c>
       <c r="R84" s="5"/>
       <c r="S84" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>22.125131923585243</v>
       </c>
       <c r="T84" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>22.125131923585243</v>
       </c>
       <c r="U84" s="1">
@@ -9754,7 +9776,7 @@
       </c>
       <c r="AC84" s="1"/>
       <c r="AD84" s="1">
-        <f>G84*R84</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AE84" s="1"/>
@@ -9779,10 +9801,10 @@
     </row>
     <row r="85" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C85" s="1">
         <v>1038.414</v>
@@ -9801,14 +9823,14 @@
       </c>
       <c r="H85" s="1"/>
       <c r="I85" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J85" s="1"/>
       <c r="K85" s="1">
         <v>1495</v>
       </c>
       <c r="L85" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>-55.119999999999891</v>
       </c>
       <c r="M85" s="1"/>
@@ -9820,19 +9842,19 @@
         <v>1242.213958</v>
       </c>
       <c r="Q85" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>287.976</v>
       </c>
       <c r="R85" s="5">
+        <f t="shared" ref="R85:R86" si="17">$R$1*Q85-P85-O85-F85</f>
+        <v>823.6847919199995</v>
+      </c>
+      <c r="S85" s="1">
         <f t="shared" si="13"/>
-        <v>161.33999191999919</v>
-      </c>
-      <c r="S85" s="1">
-        <f t="shared" si="11"/>
-        <v>11</v>
+        <v>13.3</v>
       </c>
       <c r="T85" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>10.439745006806126</v>
       </c>
       <c r="U85" s="1">
@@ -9861,8 +9883,8 @@
       </c>
       <c r="AC85" s="1"/>
       <c r="AD85" s="1">
-        <f>G85*R85</f>
-        <v>161.33999191999919</v>
+        <f t="shared" si="15"/>
+        <v>824</v>
       </c>
       <c r="AE85" s="1"/>
       <c r="AF85" s="1"/>
@@ -9886,10 +9908,10 @@
     </row>
     <row r="86" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C86" s="1">
         <v>1230.056</v>
@@ -9908,14 +9930,14 @@
       </c>
       <c r="H86" s="1"/>
       <c r="I86" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J86" s="1"/>
       <c r="K86" s="1">
         <v>1822.8</v>
       </c>
       <c r="L86" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>-75.33400000000006</v>
       </c>
       <c r="M86" s="1"/>
@@ -9927,16 +9949,19 @@
         <v>1412.6137160000001</v>
       </c>
       <c r="Q86" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>349.4932</v>
       </c>
-      <c r="R86" s="5"/>
+      <c r="R86" s="5">
+        <f t="shared" si="17"/>
+        <v>254.10316464000061</v>
+      </c>
       <c r="S86" s="1">
-        <f t="shared" si="11"/>
-        <v>12.572938172645419</v>
+        <f t="shared" si="13"/>
+        <v>13.3</v>
       </c>
       <c r="T86" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>12.572938172645419</v>
       </c>
       <c r="U86" s="1">
@@ -9965,8 +9990,8 @@
       </c>
       <c r="AC86" s="1"/>
       <c r="AD86" s="1">
-        <f>G86*R86</f>
-        <v>0</v>
+        <f t="shared" si="15"/>
+        <v>254</v>
       </c>
       <c r="AE86" s="1"/>
       <c r="AF86" s="1"/>
@@ -9990,10 +10015,10 @@
     </row>
     <row r="87" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C87" s="1">
         <v>2007.107</v>
@@ -10012,14 +10037,14 @@
       </c>
       <c r="H87" s="1"/>
       <c r="I87" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="J87" s="1"/>
       <c r="K87" s="1">
         <v>2433.5</v>
       </c>
       <c r="L87" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>-84.407999999999902</v>
       </c>
       <c r="M87" s="1"/>
@@ -10031,16 +10056,16 @@
         <v>154.85404799999989</v>
       </c>
       <c r="Q87" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>469.8184</v>
       </c>
       <c r="R87" s="5"/>
       <c r="S87" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>14.339398231486891</v>
       </c>
       <c r="T87" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>14.339398231486891</v>
       </c>
       <c r="U87" s="1">
@@ -10069,7 +10094,7 @@
       </c>
       <c r="AC87" s="1"/>
       <c r="AD87" s="1">
-        <f>G87*R87</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AE87" s="1"/>
@@ -10094,10 +10119,10 @@
     </row>
     <row r="88" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C88" s="1">
         <v>12</v>
@@ -10116,14 +10141,14 @@
       </c>
       <c r="H88" s="1"/>
       <c r="I88" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="J88" s="1"/>
       <c r="K88" s="1">
         <v>148</v>
       </c>
       <c r="L88" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>-108</v>
       </c>
       <c r="M88" s="1"/>
@@ -10131,16 +10156,16 @@
       <c r="O88" s="1"/>
       <c r="P88" s="1"/>
       <c r="Q88" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>8</v>
       </c>
       <c r="R88" s="5"/>
       <c r="S88" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>25.25</v>
       </c>
       <c r="T88" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>25.25</v>
       </c>
       <c r="U88" s="1">
@@ -10169,7 +10194,7 @@
       </c>
       <c r="AC88" s="1"/>
       <c r="AD88" s="1">
-        <f>G88*R88</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AE88" s="1"/>
@@ -10194,10 +10219,10 @@
     </row>
     <row r="89" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C89" s="1">
         <v>107</v>
@@ -10216,14 +10241,14 @@
       </c>
       <c r="H89" s="1"/>
       <c r="I89" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="J89" s="1"/>
       <c r="K89" s="1">
         <v>51</v>
       </c>
       <c r="L89" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>-5</v>
       </c>
       <c r="M89" s="1"/>
@@ -10233,16 +10258,16 @@
         <v>44.800000000000011</v>
       </c>
       <c r="Q89" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>9.1999999999999993</v>
       </c>
       <c r="R89" s="5"/>
       <c r="S89" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>13.89130434782609</v>
       </c>
       <c r="T89" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>13.89130434782609</v>
       </c>
       <c r="U89" s="1">
@@ -10271,7 +10296,7 @@
       </c>
       <c r="AC89" s="1"/>
       <c r="AD89" s="1">
-        <f>G89*R89</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AE89" s="1"/>
@@ -10296,10 +10321,10 @@
     </row>
     <row r="90" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C90" s="1">
         <v>73</v>
@@ -10323,7 +10348,7 @@
         <v>59</v>
       </c>
       <c r="L90" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>-9</v>
       </c>
       <c r="M90" s="1"/>
@@ -10335,16 +10360,16 @@
         <v>99.680000000000021</v>
       </c>
       <c r="Q90" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="R90" s="5"/>
       <c r="S90" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>16.68</v>
       </c>
       <c r="T90" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>16.68</v>
       </c>
       <c r="U90" s="1">
@@ -10373,7 +10398,7 @@
       </c>
       <c r="AC90" s="1"/>
       <c r="AD90" s="1">
-        <f>G90*R90</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AE90" s="1"/>
@@ -10398,10 +10423,10 @@
     </row>
     <row r="91" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C91" s="1">
         <v>45</v>
@@ -10420,14 +10445,14 @@
       </c>
       <c r="H91" s="1"/>
       <c r="I91" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="J91" s="1"/>
       <c r="K91" s="1">
         <v>41</v>
       </c>
       <c r="L91" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>-16</v>
       </c>
       <c r="M91" s="1"/>
@@ -10439,16 +10464,16 @@
         <v>61.000000000000007</v>
       </c>
       <c r="Q91" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>5</v>
       </c>
       <c r="R91" s="5"/>
       <c r="S91" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>27.560000000000002</v>
       </c>
       <c r="T91" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>27.560000000000002</v>
       </c>
       <c r="U91" s="1">
@@ -10477,7 +10502,7 @@
       </c>
       <c r="AC91" s="1"/>
       <c r="AD91" s="1">
-        <f>G91*R91</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AE91" s="1"/>
@@ -10502,10 +10527,10 @@
     </row>
     <row r="92" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C92" s="1">
         <v>92</v>
@@ -10524,14 +10549,14 @@
       </c>
       <c r="H92" s="1"/>
       <c r="I92" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="J92" s="1"/>
       <c r="K92" s="1">
         <v>78</v>
       </c>
       <c r="L92" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>-2</v>
       </c>
       <c r="M92" s="1"/>
@@ -10543,16 +10568,16 @@
         <v>155.19999999999999</v>
       </c>
       <c r="Q92" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>15.2</v>
       </c>
       <c r="R92" s="5"/>
       <c r="S92" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>15.210526315789474</v>
       </c>
       <c r="T92" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>15.210526315789474</v>
       </c>
       <c r="U92" s="1">
@@ -10581,7 +10606,7 @@
       </c>
       <c r="AC92" s="1"/>
       <c r="AD92" s="1">
-        <f>G92*R92</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AE92" s="1"/>
@@ -10606,10 +10631,10 @@
     </row>
     <row r="93" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A93" s="14" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B93" s="14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C93" s="14">
         <v>-2</v>
@@ -10628,14 +10653,14 @@
       </c>
       <c r="H93" s="14"/>
       <c r="I93" s="14" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J93" s="14"/>
       <c r="K93" s="14">
         <v>6</v>
       </c>
       <c r="L93" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>-11</v>
       </c>
       <c r="M93" s="14"/>
@@ -10647,16 +10672,16 @@
         <v>0</v>
       </c>
       <c r="Q93" s="14">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>-1</v>
       </c>
       <c r="R93" s="16"/>
       <c r="S93" s="14">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>-33.188000000000002</v>
       </c>
       <c r="T93" s="14">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>-33.188000000000002</v>
       </c>
       <c r="U93" s="14">
@@ -10684,10 +10709,10 @@
         <v>12.6</v>
       </c>
       <c r="AC93" s="14" t="s">
-        <v>212</v>
-      </c>
-      <c r="AD93" s="14">
-        <f>G93*R93</f>
+        <v>211</v>
+      </c>
+      <c r="AD93" s="1">
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AE93" s="1"/>
@@ -10712,10 +10737,10 @@
     </row>
     <row r="94" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A94" s="14" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B94" s="14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C94" s="14">
         <v>35</v>
@@ -10734,14 +10759,14 @@
       </c>
       <c r="H94" s="14"/>
       <c r="I94" s="14" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="J94" s="14"/>
       <c r="K94" s="14">
         <v>42</v>
       </c>
       <c r="L94" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>-3</v>
       </c>
       <c r="M94" s="14"/>
@@ -10753,16 +10778,16 @@
         <v>0</v>
       </c>
       <c r="Q94" s="14">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>7.8</v>
       </c>
       <c r="R94" s="16"/>
       <c r="S94" s="14">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>13.241025641025642</v>
       </c>
       <c r="T94" s="14">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>13.241025641025642</v>
       </c>
       <c r="U94" s="14">
@@ -10790,10 +10815,10 @@
         <v>10.8</v>
       </c>
       <c r="AC94" s="14" t="s">
-        <v>212</v>
-      </c>
-      <c r="AD94" s="14">
-        <f>G94*R94</f>
+        <v>211</v>
+      </c>
+      <c r="AD94" s="1">
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AE94" s="1"/>
@@ -10818,10 +10843,10 @@
     </row>
     <row r="95" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A95" s="11" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B95" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C95" s="11">
         <v>166.39400000000001</v>
@@ -10840,14 +10865,14 @@
       </c>
       <c r="H95" s="11"/>
       <c r="I95" s="11" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J95" s="11"/>
       <c r="K95" s="11">
         <v>45.6</v>
       </c>
       <c r="L95" s="11">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>5.5300000000000011</v>
       </c>
       <c r="M95" s="11"/>
@@ -10855,16 +10880,16 @@
       <c r="O95" s="11"/>
       <c r="P95" s="11"/>
       <c r="Q95" s="11">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>10.226000000000001</v>
       </c>
       <c r="R95" s="13"/>
       <c r="S95" s="11">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>12.060825347154312</v>
       </c>
       <c r="T95" s="11">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>12.060825347154312</v>
       </c>
       <c r="U95" s="11">
@@ -10892,9 +10917,12 @@
         <v>0</v>
       </c>
       <c r="AC95" s="11" t="s">
-        <v>217</v>
-      </c>
-      <c r="AD95" s="11"/>
+        <v>216</v>
+      </c>
+      <c r="AD95" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AE95" s="1"/>
       <c r="AF95" s="1"/>
       <c r="AG95" s="1"/>
@@ -10917,10 +10945,10 @@
     </row>
     <row r="96" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C96" s="1">
         <v>16</v>
@@ -10939,14 +10967,14 @@
       </c>
       <c r="H96" s="1"/>
       <c r="I96" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="J96" s="1"/>
       <c r="K96" s="1">
         <v>39</v>
       </c>
       <c r="L96" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>-34</v>
       </c>
       <c r="M96" s="1"/>
@@ -10956,16 +10984,16 @@
       </c>
       <c r="P96" s="1"/>
       <c r="Q96" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="R96" s="5"/>
       <c r="S96" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>169.84</v>
       </c>
       <c r="T96" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>169.84</v>
       </c>
       <c r="U96" s="1">
@@ -10994,7 +11022,7 @@
       </c>
       <c r="AC96" s="1"/>
       <c r="AD96" s="1">
-        <f>G96*R96</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AE96" s="1"/>
@@ -11019,10 +11047,10 @@
     </row>
     <row r="97" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C97" s="1">
         <v>146</v>
@@ -11041,14 +11069,14 @@
       </c>
       <c r="H97" s="1"/>
       <c r="I97" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="J97" s="1"/>
       <c r="K97" s="1">
         <v>85</v>
       </c>
       <c r="L97" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>-4</v>
       </c>
       <c r="M97" s="1"/>
@@ -11058,16 +11086,16 @@
         <v>74.399999999999977</v>
       </c>
       <c r="Q97" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>16.2</v>
       </c>
       <c r="R97" s="5"/>
       <c r="S97" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>12.061728395061728</v>
       </c>
       <c r="T97" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>12.061728395061728</v>
       </c>
       <c r="U97" s="1">
@@ -11096,7 +11124,7 @@
       </c>
       <c r="AC97" s="1"/>
       <c r="AD97" s="1">
-        <f>G97*R97</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AE97" s="1"/>
@@ -11121,10 +11149,10 @@
     </row>
     <row r="98" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C98" s="1">
         <v>330.017</v>
@@ -11143,14 +11171,14 @@
       </c>
       <c r="H98" s="1"/>
       <c r="I98" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="J98" s="1"/>
       <c r="K98" s="1">
         <v>217.28299999999999</v>
       </c>
       <c r="L98" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>4.0430000000000064</v>
       </c>
       <c r="M98" s="1"/>
@@ -11162,16 +11190,16 @@
         <v>191.9909200000001</v>
       </c>
       <c r="Q98" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>44.2652</v>
       </c>
       <c r="R98" s="5"/>
       <c r="S98" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>13.744033687863153</v>
       </c>
       <c r="T98" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>13.744033687863153</v>
       </c>
       <c r="U98" s="1">
@@ -11200,7 +11228,7 @@
       </c>
       <c r="AC98" s="1"/>
       <c r="AD98" s="1">
-        <f>G98*R98</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AE98" s="1"/>
@@ -11225,10 +11253,10 @@
     </row>
     <row r="99" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C99" s="1">
         <v>146.393</v>
@@ -11247,14 +11275,14 @@
       </c>
       <c r="H99" s="1"/>
       <c r="I99" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="J99" s="1"/>
       <c r="K99" s="1">
         <v>206.22</v>
       </c>
       <c r="L99" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>4.2860000000000014</v>
       </c>
       <c r="M99" s="1"/>
@@ -11264,16 +11292,16 @@
       </c>
       <c r="P99" s="1"/>
       <c r="Q99" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>42.101199999999999</v>
       </c>
       <c r="R99" s="5"/>
       <c r="S99" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>14.811609751741042</v>
       </c>
       <c r="T99" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>14.811609751741042</v>
       </c>
       <c r="U99" s="1">
@@ -11302,7 +11330,7 @@
       </c>
       <c r="AC99" s="1"/>
       <c r="AD99" s="1">
-        <f>G99*R99</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AE99" s="1"/>
@@ -11327,10 +11355,10 @@
     </row>
     <row r="100" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C100" s="1">
         <v>75.224000000000004</v>
@@ -11349,14 +11377,14 @@
       </c>
       <c r="H100" s="1"/>
       <c r="I100" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="J100" s="1"/>
       <c r="K100" s="1">
         <v>230.02</v>
       </c>
       <c r="L100" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>-5.6370000000000005</v>
       </c>
       <c r="M100" s="1"/>
@@ -11366,16 +11394,16 @@
       </c>
       <c r="P100" s="1"/>
       <c r="Q100" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>44.876600000000003</v>
       </c>
       <c r="R100" s="5"/>
       <c r="S100" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>13.642426565292379</v>
       </c>
       <c r="T100" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>13.642426565292379</v>
       </c>
       <c r="U100" s="1">
@@ -11404,7 +11432,7 @@
       </c>
       <c r="AC100" s="1"/>
       <c r="AD100" s="1">
-        <f>G100*R100</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AE100" s="1"/>
@@ -11429,10 +11457,10 @@
     </row>
     <row r="101" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C101" s="1">
         <v>4</v>
@@ -11451,14 +11479,14 @@
       </c>
       <c r="H101" s="1"/>
       <c r="I101" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="J101" s="1"/>
       <c r="K101" s="1">
         <v>103</v>
       </c>
       <c r="L101" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>-116</v>
       </c>
       <c r="M101" s="1"/>
@@ -11468,16 +11496,16 @@
         <v>100</v>
       </c>
       <c r="Q101" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>-2.6</v>
       </c>
       <c r="R101" s="5"/>
       <c r="S101" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>-116.92307692307692</v>
       </c>
       <c r="T101" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>-116.92307692307692</v>
       </c>
       <c r="U101" s="1">
@@ -11506,7 +11534,7 @@
       </c>
       <c r="AC101" s="1"/>
       <c r="AD101" s="1">
-        <f>G101*R101</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AE101" s="1"/>
@@ -11531,10 +11559,10 @@
     </row>
     <row r="102" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C102" s="1">
         <v>108</v>
@@ -11558,7 +11586,7 @@
         <v>128</v>
       </c>
       <c r="L102" s="1">
-        <f t="shared" ref="L102:L114" si="14">E102-K102</f>
+        <f t="shared" ref="L102:L114" si="18">E102-K102</f>
         <v>-8</v>
       </c>
       <c r="M102" s="1"/>
@@ -11570,16 +11598,16 @@
         <v>239.44</v>
       </c>
       <c r="Q102" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>24</v>
       </c>
       <c r="R102" s="5"/>
       <c r="S102" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>19.983333333333334</v>
       </c>
       <c r="T102" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>19.983333333333334</v>
       </c>
       <c r="U102" s="1">
@@ -11608,7 +11636,7 @@
       </c>
       <c r="AC102" s="1"/>
       <c r="AD102" s="1">
-        <f>G102*R102</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AE102" s="1"/>
@@ -11633,10 +11661,10 @@
     </row>
     <row r="103" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C103" s="1">
         <v>248</v>
@@ -11655,14 +11683,14 @@
       </c>
       <c r="H103" s="1"/>
       <c r="I103" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J103" s="1"/>
       <c r="K103" s="1">
         <v>160</v>
       </c>
       <c r="L103" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>-22</v>
       </c>
       <c r="M103" s="1"/>
@@ -11674,16 +11702,16 @@
         <v>83.079999999999927</v>
       </c>
       <c r="Q103" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>27.6</v>
       </c>
       <c r="R103" s="5"/>
       <c r="S103" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>18.391304347826082</v>
       </c>
       <c r="T103" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>18.391304347826082</v>
       </c>
       <c r="U103" s="1">
@@ -11712,7 +11740,7 @@
       </c>
       <c r="AC103" s="1"/>
       <c r="AD103" s="1">
-        <f>G103*R103</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AE103" s="1"/>
@@ -11737,10 +11765,10 @@
     </row>
     <row r="104" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C104" s="1">
         <v>99.400999999999996</v>
@@ -11759,14 +11787,14 @@
       </c>
       <c r="H104" s="1"/>
       <c r="I104" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J104" s="1"/>
       <c r="K104" s="1">
         <v>111.4</v>
       </c>
       <c r="L104" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>-90.749000000000009</v>
       </c>
       <c r="M104" s="1"/>
@@ -11778,16 +11806,16 @@
         <v>46.858640000000022</v>
       </c>
       <c r="Q104" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>4.1302000000000003</v>
       </c>
       <c r="R104" s="5"/>
       <c r="S104" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>76.165173599341443</v>
       </c>
       <c r="T104" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>76.165173599341443</v>
       </c>
       <c r="U104" s="1">
@@ -11816,7 +11844,7 @@
       </c>
       <c r="AC104" s="1"/>
       <c r="AD104" s="1">
-        <f>G104*R104</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AE104" s="1"/>
@@ -11841,10 +11869,10 @@
     </row>
     <row r="105" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C105" s="1">
         <v>5.1189999999999998</v>
@@ -11863,14 +11891,14 @@
       </c>
       <c r="H105" s="1"/>
       <c r="I105" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J105" s="1"/>
       <c r="K105" s="1">
         <v>70</v>
       </c>
       <c r="L105" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>-49.42</v>
       </c>
       <c r="M105" s="1"/>
@@ -11878,16 +11906,16 @@
       <c r="O105" s="1"/>
       <c r="P105" s="1"/>
       <c r="Q105" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>4.1159999999999997</v>
       </c>
       <c r="R105" s="5"/>
       <c r="S105" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>46.771865889212833</v>
       </c>
       <c r="T105" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>46.771865889212833</v>
       </c>
       <c r="U105" s="1">
@@ -11916,7 +11944,7 @@
       </c>
       <c r="AC105" s="1"/>
       <c r="AD105" s="1">
-        <f>G105*R105</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AE105" s="1"/>
@@ -11941,10 +11969,10 @@
     </row>
     <row r="106" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C106" s="1">
         <v>-2.4420000000000002</v>
@@ -11964,7 +11992,7 @@
       <c r="J106" s="1"/>
       <c r="K106" s="1"/>
       <c r="L106" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="M106" s="1"/>
@@ -11972,16 +12000,16 @@
       <c r="O106" s="1"/>
       <c r="P106" s="1"/>
       <c r="Q106" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="R106" s="5"/>
       <c r="S106" s="1" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T106" s="1" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U106" s="1">
@@ -12010,7 +12038,7 @@
       </c>
       <c r="AC106" s="1"/>
       <c r="AD106" s="1">
-        <f>G106*R106</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AE106" s="1"/>
@@ -12035,10 +12063,10 @@
     </row>
     <row r="107" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C107" s="1">
         <v>189.57</v>
@@ -12057,14 +12085,14 @@
       </c>
       <c r="H107" s="1"/>
       <c r="I107" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="J107" s="1"/>
       <c r="K107" s="1">
         <v>183.1</v>
       </c>
       <c r="L107" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>6.6640000000000157</v>
       </c>
       <c r="M107" s="1"/>
@@ -12072,19 +12100,19 @@
       <c r="O107" s="1"/>
       <c r="P107" s="1"/>
       <c r="Q107" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>37.952800000000003</v>
       </c>
       <c r="R107" s="5">
-        <f t="shared" ref="R96:R114" si="15">11*Q107-P107-O107-F107</f>
+        <f t="shared" ref="R107" si="19">11*Q107-P107-O107-F107</f>
         <v>122.09180000000003</v>
       </c>
       <c r="S107" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>11</v>
       </c>
       <c r="T107" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>7.7830621192639278</v>
       </c>
       <c r="U107" s="1">
@@ -12113,8 +12141,8 @@
       </c>
       <c r="AC107" s="1"/>
       <c r="AD107" s="1">
-        <f>G107*R107</f>
-        <v>122.09180000000003</v>
+        <f t="shared" si="15"/>
+        <v>122</v>
       </c>
       <c r="AE107" s="1"/>
       <c r="AF107" s="1"/>
@@ -12138,10 +12166,10 @@
     </row>
     <row r="108" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C108" s="1">
         <v>57.81</v>
@@ -12160,14 +12188,14 @@
       </c>
       <c r="H108" s="1"/>
       <c r="I108" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="J108" s="1"/>
       <c r="K108" s="1">
         <v>44.9</v>
       </c>
       <c r="L108" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>-2.9709999999999965</v>
       </c>
       <c r="M108" s="1"/>
@@ -12177,16 +12205,16 @@
       </c>
       <c r="P108" s="1"/>
       <c r="Q108" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>8.3857999999999997</v>
       </c>
       <c r="R108" s="5"/>
       <c r="S108" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>20.84816713968852</v>
       </c>
       <c r="T108" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>20.84816713968852</v>
       </c>
       <c r="U108" s="1">
@@ -12215,7 +12243,7 @@
       </c>
       <c r="AC108" s="1"/>
       <c r="AD108" s="1">
-        <f>G108*R108</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AE108" s="1"/>
@@ -12240,10 +12268,10 @@
     </row>
     <row r="109" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C109" s="1">
         <v>868.25599999999997</v>
@@ -12267,7 +12295,7 @@
         <v>216.4</v>
       </c>
       <c r="L109" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>-27.399000000000001</v>
       </c>
       <c r="M109" s="1"/>
@@ -12275,16 +12303,16 @@
       <c r="O109" s="1"/>
       <c r="P109" s="1"/>
       <c r="Q109" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>37.800200000000004</v>
       </c>
       <c r="R109" s="5"/>
       <c r="S109" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>61.291130734758013</v>
       </c>
       <c r="T109" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>61.291130734758013</v>
       </c>
       <c r="U109" s="1">
@@ -12312,10 +12340,10 @@
         <v>0</v>
       </c>
       <c r="AC109" s="18" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AD109" s="1">
-        <f>G109*R109</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AE109" s="1"/>
@@ -12340,10 +12368,10 @@
     </row>
     <row r="110" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C110" s="1">
         <v>163</v>
@@ -12362,14 +12390,14 @@
       </c>
       <c r="H110" s="1"/>
       <c r="I110" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="J110" s="1"/>
       <c r="K110" s="1">
         <v>200</v>
       </c>
       <c r="L110" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>-14</v>
       </c>
       <c r="M110" s="1"/>
@@ -12381,16 +12409,16 @@
         <v>65.479999999999961</v>
       </c>
       <c r="Q110" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>37.200000000000003</v>
       </c>
       <c r="R110" s="5"/>
       <c r="S110" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>14.999999999999998</v>
       </c>
       <c r="T110" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>14.999999999999998</v>
       </c>
       <c r="U110" s="1">
@@ -12419,7 +12447,7 @@
       </c>
       <c r="AC110" s="1"/>
       <c r="AD110" s="1">
-        <f>G110*R110</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AE110" s="1"/>
@@ -12444,10 +12472,10 @@
     </row>
     <row r="111" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C111" s="1">
         <v>158</v>
@@ -12464,14 +12492,14 @@
       </c>
       <c r="H111" s="1"/>
       <c r="I111" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="J111" s="1"/>
       <c r="K111" s="1">
         <v>179</v>
       </c>
       <c r="L111" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>-197</v>
       </c>
       <c r="M111" s="1"/>
@@ -12479,18 +12507,18 @@
       <c r="O111" s="1"/>
       <c r="P111" s="1"/>
       <c r="Q111" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>-3.6</v>
       </c>
       <c r="R111" s="5">
         <v>80</v>
       </c>
       <c r="S111" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>-22.222222222222221</v>
       </c>
       <c r="T111" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="U111" s="1">
@@ -12518,10 +12546,10 @@
         <v>15.2</v>
       </c>
       <c r="AC111" s="9" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AD111" s="1">
-        <f>G111*R111</f>
+        <f t="shared" si="15"/>
         <v>24</v>
       </c>
       <c r="AE111" s="1"/>
@@ -12546,10 +12574,10 @@
     </row>
     <row r="112" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C112" s="1">
         <v>-7.9000000000000001E-2</v>
@@ -12566,12 +12594,12 @@
       </c>
       <c r="H112" s="1"/>
       <c r="I112" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="J112" s="1"/>
       <c r="K112" s="1"/>
       <c r="L112" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="M112" s="1"/>
@@ -12581,16 +12609,16 @@
         <v>10</v>
       </c>
       <c r="Q112" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="R112" s="5"/>
       <c r="S112" s="1" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T112" s="1" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U112" s="1">
@@ -12619,7 +12647,7 @@
       </c>
       <c r="AC112" s="1"/>
       <c r="AD112" s="1">
-        <f>G112*R112</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AE112" s="1"/>
@@ -12644,10 +12672,10 @@
     </row>
     <row r="113" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C113" s="1">
         <v>34</v>
@@ -12666,14 +12694,14 @@
       </c>
       <c r="H113" s="1"/>
       <c r="I113" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="J113" s="1"/>
       <c r="K113" s="1">
         <v>100</v>
       </c>
       <c r="L113" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>-60</v>
       </c>
       <c r="M113" s="1"/>
@@ -12683,16 +12711,16 @@
       </c>
       <c r="P113" s="1"/>
       <c r="Q113" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>8</v>
       </c>
       <c r="R113" s="5"/>
       <c r="S113" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>32.159999999999997</v>
       </c>
       <c r="T113" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>32.159999999999997</v>
       </c>
       <c r="U113" s="1">
@@ -12721,7 +12749,7 @@
       </c>
       <c r="AC113" s="1"/>
       <c r="AD113" s="1">
-        <f>G113*R113</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AE113" s="1"/>
@@ -12746,10 +12774,10 @@
     </row>
     <row r="114" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C114" s="1">
         <v>34</v>
@@ -12768,14 +12796,14 @@
       </c>
       <c r="H114" s="1"/>
       <c r="I114" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J114" s="1"/>
       <c r="K114" s="1">
         <v>60</v>
       </c>
       <c r="L114" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>-29</v>
       </c>
       <c r="M114" s="1"/>
@@ -12787,16 +12815,16 @@
         <v>84.679999999999978</v>
       </c>
       <c r="Q114" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>6.2</v>
       </c>
       <c r="R114" s="5"/>
       <c r="S114" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>24.903225806451609</v>
       </c>
       <c r="T114" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>24.903225806451609</v>
       </c>
       <c r="U114" s="1">
@@ -12825,7 +12853,7 @@
       </c>
       <c r="AC114" s="1"/>
       <c r="AD114" s="1">
-        <f>G114*R114</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AE114" s="1"/>
